--- a/Config/GameContent.xlsx
+++ b/Config/GameContent.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17080" activeTab="2"/>
+    <workbookView windowHeight="17080" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,11 @@
     <sheet name="枚举与动作说明" sheetId="10" r:id="rId10"/>
     <sheet name="兵营" sheetId="11" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">攻击!$A$2:$G$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">技能!$A$2:$F$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">全局参数!$A$2:$D$101</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="419">
   <si>
     <t>game-td 策划配置</t>
   </si>
@@ -89,13 +94,13 @@
     <t>定义已就绪</t>
   </si>
   <si>
-    <t>技能效果、费用、建设时间、升级分支、退款规则已导出并校验；执行系统尚未接入。</t>
+    <t>英雄主动技能已接入瞬时范围扣血；通用附加效果仍仅定义。兵营费用与扩编已执行，普通建设时间与退款规则暂未执行。</t>
   </si>
   <si>
     <t>初始建议值</t>
   </si>
   <si>
-    <t>建造费用、建设时间、拆除返还、升级分支及禁用技能示例是本轮新增策划初值。</t>
+    <t>示例技能：短按空格半径4/扣血30/CD3秒，长按半径6/扣血60/CD8秒；技能表配置冷却，攻击表配置范围和伤害。</t>
   </si>
   <si>
     <t>素材规范</t>
@@ -254,6 +259,9 @@
     <t>attack.alien</t>
   </si>
   <si>
+    <t>skill.alien_burst;skill.alien_burst_heavy</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -386,10 +394,22 @@
     <t>远程射手直伤</t>
   </si>
   <si>
+    <t>attack.hero_burst</t>
+  </si>
+  <si>
+    <t>英雄震击范围伤害</t>
+  </si>
+  <si>
+    <t>attack.hero_burst_heavy</t>
+  </si>
+  <si>
+    <t>英雄强震击范围伤害</t>
+  </si>
+  <si>
     <t>技能ID</t>
   </si>
   <si>
-    <t>启用/当前执行尚未接入</t>
+    <t>启用</t>
   </si>
   <si>
     <t>冷却/秒</t>
@@ -404,39 +424,45 @@
     <t>skill.alien_burst</t>
   </si>
   <si>
-    <t>Alien爆发/设计示例</t>
+    <t>英雄震击</t>
+  </si>
+  <si>
+    <t>skill.alien_burst_heavy</t>
+  </si>
+  <si>
+    <t>英雄强震击</t>
+  </si>
+  <si>
+    <t>效果ID</t>
+  </si>
+  <si>
+    <t>效果类型</t>
+  </si>
+  <si>
+    <t>持续/秒</t>
+  </si>
+  <si>
+    <t>数值/减速比例0至1</t>
+  </si>
+  <si>
+    <t>最大层数</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>magnitude</t>
+  </si>
+  <si>
+    <t>maxStacks</t>
   </si>
   <si>
     <t>effect.slow</t>
   </si>
   <si>
-    <t>效果ID</t>
-  </si>
-  <si>
-    <t>效果类型</t>
-  </si>
-  <si>
-    <t>持续/秒</t>
-  </si>
-  <si>
-    <t>数值/减速比例0至1</t>
-  </si>
-  <si>
-    <t>最大层数</t>
-  </si>
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>magnitude</t>
-  </si>
-  <si>
-    <t>maxStacks</t>
-  </si>
-  <si>
     <t>减速/设计示例</t>
   </si>
   <si>
@@ -981,6 +1007,12 @@
   </si>
   <si>
     <t>每局初始金币。用于建造两类兵营和扩编升级，重开时恢复。正整数或0。</t>
+  </si>
+  <si>
+    <t>battle.soldierSelectionRadius</t>
+  </si>
+  <si>
+    <t>R短按与长按共用的附近士兵选择半径；白圈同步读取此值。单位：逻辑地面单位，必须大于0。</t>
   </si>
   <si>
     <t>字段/约定</t>
@@ -2686,408 +2718,408 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:4">
       <c r="A26" s="5" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:4">
       <c r="A27" s="5" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -3110,19 +3142,19 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:5">
@@ -3130,24 +3162,24 @@
         <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="4">
         <v>4</v>
@@ -3161,10 +3193,10 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="4">
         <v>4</v>
@@ -3309,21 +3341,21 @@
         <v>70</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:12">
       <c r="A4" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" s="13">
         <v>60</v>
@@ -3341,27 +3373,27 @@
         <v>1.35</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:12">
       <c r="A5" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="13">
         <v>12</v>
@@ -3379,27 +3411,27 @@
         <v>0.95</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:12">
       <c r="A6" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" s="13">
         <v>60</v>
@@ -3417,27 +3449,27 @@
         <v>0.95</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:12">
       <c r="A7" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" s="13">
         <v>10</v>
@@ -3455,16 +3487,16 @@
         <v>1</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -4801,25 +4833,25 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:7">
       <c r="A1" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:7">
@@ -4830,19 +4862,19 @@
         <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:7">
@@ -4850,10 +4882,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="13">
         <v>20</v>
@@ -4865,18 +4897,18 @@
         <v>0</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:7">
       <c r="A4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" s="13">
         <v>9</v>
@@ -4888,18 +4920,18 @@
         <v>0.15</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:7">
       <c r="A5" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="D5" s="13">
         <v>7</v>
@@ -4911,21 +4943,21 @@
         <v>0.15</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:7">
       <c r="A6" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D6" s="13">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E6" s="14">
         <v>1</v>
@@ -4934,18 +4966,18 @@
         <v>5</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:7">
       <c r="A7" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" s="13">
         <v>8</v>
@@ -4957,18 +4989,18 @@
         <v>0.35</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:7">
       <c r="A8" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D8" s="13">
         <v>6</v>
@@ -4980,26 +5012,50 @@
         <v>4.5</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="12"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:7">
+      <c r="A9" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="13">
+        <v>30</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14">
+        <v>4</v>
+      </c>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:7">
+      <c r="A10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="13">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14">
+        <v>6</v>
+      </c>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="11"/>
@@ -5812,6 +5868,9 @@
       <c r="G100" s="12"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:G100" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="不支持的配置值" error="请从列表选择，含义见“枚举与动作说明”。" sqref="C3:C1000">
       <formula1>"Contact,Melee,Direct"</formula1>
@@ -5843,22 +5902,22 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:6">
@@ -5869,45 +5928,53 @@
         <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>62</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C3" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+        <v>115</v>
+      </c>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:6">
+      <c r="A4" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14">
+        <v>8</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="11"/>
@@ -6678,6 +6745,9 @@
       <c r="F100" s="12"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:F100" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C3:C100">
       <formula1>"TRUE,FALSE"</formula1>
@@ -6704,22 +6774,22 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:6">
       <c r="A1" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:6">
@@ -6730,27 +6800,27 @@
         <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D3" s="14">
         <v>2</v>
@@ -7575,10 +7645,10 @@
         <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4">
@@ -7589,21 +7659,21 @@
         <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D3" s="9" t="b">
         <v>1</v>
@@ -7611,10 +7681,10 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4">
       <c r="A4" s="8" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>68</v>
@@ -8227,40 +8297,40 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:12">
       <c r="A1" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:12">
@@ -8271,16 +8341,16 @@
         <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>57</v>
@@ -8289,24 +8359,24 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:12">
       <c r="A3" s="8" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C3" s="13">
         <v>1</v>
@@ -8324,7 +8394,7 @@
         <v>150</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I3" s="13">
         <v>50</v>
@@ -8341,10 +8411,10 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:12">
       <c r="A4" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C4" s="13">
         <v>2</v>
@@ -8362,7 +8432,7 @@
         <v>500</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I4" s="13">
         <v>100</v>
@@ -8379,10 +8449,10 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:12">
       <c r="A5" s="8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C5" s="13">
         <v>1</v>
@@ -8400,7 +8470,7 @@
         <v>150</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I5" s="13">
         <v>100</v>
@@ -8417,10 +8487,10 @@
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:12">
       <c r="A6" s="8" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C6" s="13">
         <v>2</v>
@@ -8438,7 +8508,7 @@
         <v>150</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" s="13">
         <v>100</v>
@@ -8455,10 +8525,10 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:12">
       <c r="A7" s="8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C7" s="13">
         <v>2</v>
@@ -8476,7 +8546,7 @@
         <v>150</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" s="13">
         <v>100</v>
@@ -8493,10 +8563,10 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:12">
       <c r="A8" s="8" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C8" s="13">
         <v>2</v>
@@ -8514,7 +8584,7 @@
         <v>150</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I8" s="13">
         <v>100</v>
@@ -8531,10 +8601,10 @@
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:12">
       <c r="A9" s="8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C9" s="13">
         <v>2</v>
@@ -8552,7 +8622,7 @@
         <v>150</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" s="13">
         <v>100</v>
@@ -8569,10 +8639,10 @@
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:12">
       <c r="A10" s="8" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C10" s="13">
         <v>2</v>
@@ -8590,7 +8660,7 @@
         <v>150</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="13">
         <v>100</v>
@@ -8607,10 +8677,10 @@
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:12">
       <c r="A11" s="8" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C11" s="13">
         <v>1</v>
@@ -8628,7 +8698,7 @@
         <v>150</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I11" s="13">
         <v>100</v>
@@ -8645,10 +8715,10 @@
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:12">
       <c r="A12" s="8" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C12" s="13">
         <v>2</v>
@@ -8666,7 +8736,7 @@
         <v>150</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I12" s="13">
         <v>100</v>
@@ -8683,10 +8753,10 @@
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:12">
       <c r="A13" s="8" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C13" s="13">
         <v>2</v>
@@ -8704,7 +8774,7 @@
         <v>300</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I13" s="13">
         <v>100</v>
@@ -8721,10 +8791,10 @@
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:12">
       <c r="A14" s="8" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C14" s="13">
         <v>2</v>
@@ -8742,7 +8812,7 @@
         <v>300</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" s="13">
         <v>100</v>
@@ -9996,37 +10066,37 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:11">
       <c r="A1" s="6" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:11">
@@ -10034,51 +10104,51 @@
         <v>54</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:11">
       <c r="A3" s="8" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F3" s="13">
         <v>75</v>
@@ -10101,19 +10171,19 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:11">
       <c r="A4" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F4" s="13">
         <v>100</v>
@@ -10136,19 +10206,19 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:11">
       <c r="A5" s="8" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F5" s="13">
         <v>150</v>
@@ -10171,19 +10241,19 @@
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:11">
       <c r="A6" s="8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" s="13">
         <v>250</v>
@@ -10206,19 +10276,19 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:11">
       <c r="A7" s="8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="13">
         <v>150</v>
@@ -10241,19 +10311,19 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:11">
       <c r="A8" s="8" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F8" s="13">
         <v>250</v>
@@ -11397,7 +11467,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="51" style="1" customWidth="1"/>
@@ -11407,16 +11477,16 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:4">
       <c r="A1" s="6" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4">
@@ -11424,643 +11494,643 @@
         <v>54</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B3" s="9">
         <v>17821</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:4">
       <c r="A4" s="8" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B4" s="9">
         <v>0.02</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4">
       <c r="A5" s="8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B5" s="9">
         <v>96</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:4">
       <c r="A6" s="8" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B6" s="9">
         <v>54</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:4">
       <c r="A7" s="8" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B7" s="9">
         <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:4">
       <c r="A8" s="8" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B8" s="9">
         <v>5</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
       <c r="A9" s="8" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B9" s="9">
         <v>5</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:4">
       <c r="A10" s="8" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B10" s="9">
         <v>0.25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:4">
       <c r="A11" s="8" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B11" s="9">
         <v>0.12</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:4">
       <c r="A12" s="8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B12" s="9">
         <v>3</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:4">
       <c r="A13" s="8" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B13" s="9">
         <v>600</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B14" s="9">
         <v>400</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:4">
       <c r="A15" s="8" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B15" s="9">
         <v>1.5</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:4">
       <c r="A16" s="8" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B16" s="9">
         <v>18</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:4">
       <c r="A17" s="8" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B17" s="9">
         <v>0.75</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:4">
       <c r="A18" s="8" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B18" s="9">
         <v>2</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:4">
       <c r="A19" s="8" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B19" s="9">
         <v>0.3</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B20" s="9">
         <v>1</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:4">
       <c r="A21" s="8" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B21" s="9">
         <v>0.31</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:4">
       <c r="A22" s="8" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B22" s="9">
         <v>0.41</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:4">
       <c r="A23" s="8" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B23" s="9">
         <v>0.25</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:4">
       <c r="A24" s="8" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B24" s="9">
         <v>1</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B25" s="9">
         <v>0.3</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:4">
       <c r="A26" s="8" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B26" s="9">
         <v>0.4</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:4">
       <c r="A27" s="8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B27" s="9">
         <v>0.245</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:4">
       <c r="A28" s="8" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B28" s="9">
         <v>1</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:4">
       <c r="A29" s="8" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B29" s="9">
         <v>0.93</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:4">
       <c r="A30" s="8" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B30" s="9">
         <v>0.73</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:4">
       <c r="A31" s="8" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B31" s="9">
         <v>0.32</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:4">
       <c r="A32" s="8" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B32" s="9">
         <v>1</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:4">
       <c r="A33" s="8" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B33" s="9">
         <v>0.52</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:4">
       <c r="A34" s="8" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B34" s="9">
         <v>0.5</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:4">
       <c r="A35" s="8" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B35" s="9">
         <v>0.4</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:4">
       <c r="A36" s="8" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B36" s="9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:4">
       <c r="A37" s="8" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B37" s="9">
         <v>1</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:4">
       <c r="A38" s="8" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B38" s="9">
         <v>1</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:4">
       <c r="A39" s="8" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B39" s="9">
         <v>5</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:4">
       <c r="A40" s="8" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B40" s="9">
         <v>10</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:4">
       <c r="A41" s="8" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B41" s="9">
         <v>10</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:4">
       <c r="A42" s="8" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B42" s="9">
         <v>1</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:4">
       <c r="A43" s="8" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B43" s="9">
         <v>10</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:4">
       <c r="A44" s="8" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B44" s="9">
         <v>0.5</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1" spans="1:4">
       <c r="A45" s="8" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B45" s="9">
         <v>2</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1" spans="1:4">
       <c r="A46" s="8" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B46" s="9">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1" spans="1:4">
       <c r="A47" s="8" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B47" s="9">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -12308,27 +12378,44 @@
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:4">
       <c r="A97" s="11"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:4">
       <c r="A98" s="11"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:4">
       <c r="A99" s="11"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:4">
       <c r="A100" s="11"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
     </row>
+    <row r="101" ht="36" customHeight="1" spans="1:4">
+      <c r="A101" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B101" s="9">
+        <v>2</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:D101" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Config/GameContent.xlsx
+++ b/Config/GameContent.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="438">
   <si>
     <t>game-td 策划配置</t>
   </si>
@@ -526,6 +526,12 @@
     <t>拆除返还比例0至1</t>
   </si>
   <si>
+    <t>分类/PlayerBuildable/Decoration/BuiltIn</t>
+  </si>
+  <si>
+    <t>放置/Building/Wall/Gate/Bastion</t>
+  </si>
+  <si>
     <t>width</t>
   </si>
   <si>
@@ -550,18 +556,33 @@
     <t>refundRatio</t>
   </si>
   <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>placementKind</t>
+  </si>
+  <si>
     <t>tower</t>
   </si>
   <si>
     <t>游侠箭楼</t>
   </si>
   <si>
+    <t>PlayerBuildable</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
     <t>hall</t>
   </si>
   <si>
     <t>曙光主堡</t>
   </si>
   <si>
+    <t>BuiltIn</t>
+  </si>
+  <si>
     <t>mage</t>
   </si>
   <si>
@@ -580,6 +601,9 @@
     <t>风车农庄</t>
   </si>
   <si>
+    <t>Decoration</t>
+  </si>
+  <si>
     <t>house</t>
   </si>
   <si>
@@ -622,6 +646,33 @@
     <t>远程兵营</t>
   </si>
   <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>城墙</t>
+  </si>
+  <si>
+    <t>Wall</t>
+  </si>
+  <si>
+    <t>gate</t>
+  </si>
+  <si>
+    <t>城门</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>bastion</t>
+  </si>
+  <si>
+    <t>敌台</t>
+  </si>
+  <si>
+    <t>Bastion</t>
+  </si>
+  <si>
     <t>升级ID</t>
   </si>
   <si>
@@ -679,7 +730,7 @@
     <t>upgrade.tower.rapid</t>
   </si>
   <si>
-    <t>连射路线/设计示例</t>
+    <t>连射路线</t>
   </si>
   <si>
     <t>tower.branch</t>
@@ -688,7 +739,7 @@
     <t>upgrade.tower.heavy</t>
   </si>
   <si>
-    <t>重弩路线/设计示例</t>
+    <t>重弩路线</t>
   </si>
   <si>
     <t>upgrade.barracks.melee.2</t>
@@ -713,6 +764,12 @@
   </si>
   <si>
     <t>远程兵营3级</t>
+  </si>
+  <si>
+    <t>upgrade.hall.2</t>
+  </si>
+  <si>
+    <t>主堡加固</t>
   </si>
   <si>
     <t>配置路径/勿改键名</t>
@@ -2718,408 +2775,408 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>108</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>139</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:4">
       <c r="A26" s="5" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:4">
       <c r="A27" s="5" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -3145,16 +3202,16 @@
         <v>148</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:5">
@@ -3162,21 +3219,21 @@
         <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>84</v>
@@ -3193,7 +3250,7 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>89</v>
@@ -8286,16 +8343,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="27" style="1" customWidth="1"/>
     <col min="3" max="7" width="19" style="1" customWidth="1"/>
     <col min="8" max="8" width="27" style="1" customWidth="1"/>
     <col min="9" max="12" width="19" style="1" customWidth="1"/>
+    <col min="13" max="14" width="30" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="44" customHeight="1" spans="1:12">
+    <row r="1" ht="44" customHeight="1" spans="1:14">
       <c r="A1" s="6" t="s">
         <v>148</v>
       </c>
@@ -8332,8 +8390,14 @@
       <c r="L1" s="6" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:12">
+      <c r="M1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:14">
       <c r="A2" s="7" t="s">
         <v>54</v>
       </c>
@@ -8341,16 +8405,16 @@
         <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>57</v>
@@ -8359,24 +8423,30 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:12">
+        <v>168</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:14">
       <c r="A3" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C3" s="13">
         <v>1</v>
@@ -8408,13 +8478,19 @@
       <c r="L3" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:12">
+      <c r="M3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:14">
       <c r="A4" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C4" s="13">
         <v>2</v>
@@ -8446,13 +8522,19 @@
       <c r="L4" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:12">
+      <c r="M4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:14">
       <c r="A5" s="8" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C5" s="13">
         <v>1</v>
@@ -8484,13 +8566,19 @@
       <c r="L5" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="1:12">
+      <c r="M5" t="s">
+        <v>173</v>
+      </c>
+      <c r="N5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="1:14">
       <c r="A6" s="8" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C6" s="13">
         <v>2</v>
@@ -8522,13 +8610,19 @@
       <c r="L6" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="1:12">
+      <c r="M6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="1:14">
       <c r="A7" s="8" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C7" s="13">
         <v>2</v>
@@ -8555,18 +8649,24 @@
         <v>0</v>
       </c>
       <c r="K7" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" ht="26" customHeight="1" spans="1:12">
+      <c r="M7" t="s">
+        <v>184</v>
+      </c>
+      <c r="N7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C8" s="13">
         <v>2</v>
@@ -8593,18 +8693,24 @@
         <v>0</v>
       </c>
       <c r="K8" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:12">
+      <c r="M8" t="s">
+        <v>184</v>
+      </c>
+      <c r="N8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:14">
       <c r="A9" s="8" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C9" s="13">
         <v>2</v>
@@ -8631,18 +8737,24 @@
         <v>0</v>
       </c>
       <c r="K9" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:12">
+      <c r="M9" t="s">
+        <v>184</v>
+      </c>
+      <c r="N9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:14">
       <c r="A10" s="8" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C10" s="13">
         <v>2</v>
@@ -8669,18 +8781,24 @@
         <v>0</v>
       </c>
       <c r="K10" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="11" ht="26" customHeight="1" spans="1:12">
+      <c r="M10" t="s">
+        <v>184</v>
+      </c>
+      <c r="N10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:14">
       <c r="A11" s="8" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C11" s="13">
         <v>1</v>
@@ -8707,18 +8825,24 @@
         <v>0</v>
       </c>
       <c r="K11" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="12" ht="26" customHeight="1" spans="1:12">
+      <c r="M11" t="s">
+        <v>184</v>
+      </c>
+      <c r="N11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C12" s="13">
         <v>2</v>
@@ -8745,18 +8869,24 @@
         <v>0</v>
       </c>
       <c r="K12" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:12">
+      <c r="M12" t="s">
+        <v>184</v>
+      </c>
+      <c r="N12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:14">
       <c r="A13" s="8" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C13" s="13">
         <v>2</v>
@@ -8788,13 +8918,19 @@
       <c r="L13" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" ht="26" customHeight="1" spans="1:12">
+      <c r="M13" t="s">
+        <v>173</v>
+      </c>
+      <c r="N13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1" spans="1:14">
       <c r="A14" s="8" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C14" s="13">
         <v>2</v>
@@ -8826,1210 +8962,144 @@
       <c r="L14" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="16"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="16"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="16"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="16"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="16"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="16"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="16"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="16"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="16"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="16"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="16"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="16"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="16"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="16"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="16"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="16"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="16"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="16"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="16"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="16"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="16"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="16"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="16"/>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="16"/>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="16"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="16"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="16"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="16"/>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="16"/>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="16"/>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="16"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="16"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="16"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="16"/>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="16"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="16"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="16"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="16"/>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="16"/>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="12"/>
-      <c r="L55" s="16"/>
-    </row>
-    <row r="56" spans="1:12">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="16"/>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="16"/>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="16"/>
-    </row>
-    <row r="59" spans="1:12">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="16"/>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="12"/>
-      <c r="L60" s="16"/>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="16"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="16"/>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="16"/>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="16"/>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="16"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="16"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="16"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="16"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="16"/>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="12"/>
-      <c r="L68" s="16"/>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="16"/>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="12"/>
-      <c r="L70" s="16"/>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="16"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="12"/>
-      <c r="L72" s="16"/>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="16"/>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="12"/>
-      <c r="L74" s="16"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="16"/>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="12"/>
-      <c r="L76" s="16"/>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="12"/>
-      <c r="L77" s="16"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="12"/>
-      <c r="L78" s="16"/>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="12"/>
-      <c r="L79" s="16"/>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="12"/>
-      <c r="L80" s="16"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" s="11"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="16"/>
-      <c r="K81" s="12"/>
-      <c r="L81" s="16"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="16"/>
-      <c r="K82" s="12"/>
-      <c r="L82" s="16"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="16"/>
-      <c r="K83" s="12"/>
-      <c r="L83" s="16"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="16"/>
-      <c r="K84" s="12"/>
-      <c r="L84" s="16"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="11"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="12"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="16"/>
-      <c r="K85" s="12"/>
-      <c r="L85" s="16"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="16"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="16"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" s="11"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="12"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="16"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="16"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="12"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="16"/>
-      <c r="K88" s="12"/>
-      <c r="L88" s="16"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="A89" s="11"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="12"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="16"/>
-      <c r="K89" s="12"/>
-      <c r="L89" s="16"/>
-    </row>
-    <row r="90" spans="1:12">
-      <c r="A90" s="11"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="12"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="12"/>
-      <c r="L90" s="16"/>
-    </row>
-    <row r="91" spans="1:12">
-      <c r="A91" s="11"/>
-      <c r="B91" s="12"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="12"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="12"/>
-      <c r="L91" s="16"/>
-    </row>
-    <row r="92" spans="1:12">
-      <c r="A92" s="11"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="12"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="12"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="16"/>
-      <c r="K92" s="12"/>
-      <c r="L92" s="16"/>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="A93" s="11"/>
-      <c r="B93" s="12"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="12"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="16"/>
-      <c r="K93" s="12"/>
-      <c r="L93" s="16"/>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="A94" s="11"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="12"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="16"/>
-      <c r="K94" s="12"/>
-      <c r="L94" s="16"/>
-    </row>
-    <row r="95" spans="1:12">
-      <c r="A95" s="11"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="12"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="16"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="16"/>
-    </row>
-    <row r="96" spans="1:12">
-      <c r="A96" s="11"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="12"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="16"/>
-      <c r="K96" s="12"/>
-      <c r="L96" s="16"/>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97" s="11"/>
-      <c r="B97" s="12"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="12"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="16"/>
-      <c r="K97" s="12"/>
-      <c r="L97" s="16"/>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" s="11"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="12"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="16"/>
-      <c r="K98" s="12"/>
-      <c r="L98" s="16"/>
-    </row>
-    <row r="99" spans="1:12">
-      <c r="A99" s="11"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="12"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="16"/>
-      <c r="K99" s="12"/>
-      <c r="L99" s="16"/>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" s="11"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="12"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="16"/>
-      <c r="K100" s="12"/>
-      <c r="L100" s="16"/>
+      <c r="M14" t="s">
+        <v>173</v>
+      </c>
+      <c r="N14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13">
+        <v>30000</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="13">
+        <v>10</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>173</v>
+      </c>
+      <c r="N15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:14">
+      <c r="A16" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="13">
+        <v>4</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13">
+        <v>100</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" s="13">
+        <v>60</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="M16" t="s">
+        <v>173</v>
+      </c>
+      <c r="N16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:14">
+      <c r="A17" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="13">
+        <v>2</v>
+      </c>
+      <c r="D17" s="13">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13">
+        <v>500</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="13">
+        <v>100</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="s">
+        <v>173</v>
+      </c>
+      <c r="N17" t="s">
+        <v>207</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -10053,7 +9123,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="43" style="1" customWidth="1"/>
@@ -10066,7 +9136,7 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:11">
       <c r="A1" s="6" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>148</v>
@@ -10075,28 +9145,28 @@
         <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:11">
@@ -10104,51 +9174,51 @@
         <v>54</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:11">
       <c r="A3" s="8" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F3" s="13">
         <v>75</v>
@@ -10171,19 +9241,19 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:11">
       <c r="A4" s="8" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F4" s="13">
         <v>100</v>
@@ -10206,13 +9276,13 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:11">
       <c r="A5" s="8" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>71</v>
@@ -10241,16 +9311,16 @@
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:11">
       <c r="A6" s="8" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>71</v>
@@ -10276,13 +9346,13 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:11">
       <c r="A7" s="8" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>71</v>
@@ -10311,16 +9381,16 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:11">
       <c r="A8" s="8" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>71</v>
@@ -11400,7 +10470,7 @@
       <c r="I96" s="15"/>
       <c r="J96" s="16"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:11">
       <c r="A97" s="11"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -11412,7 +10482,7 @@
       <c r="I97" s="15"/>
       <c r="J97" s="16"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:11">
       <c r="A98" s="11"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
@@ -11424,7 +10494,7 @@
       <c r="I98" s="15"/>
       <c r="J98" s="16"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:11">
       <c r="A99" s="11"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
@@ -11436,7 +10506,7 @@
       <c r="I99" s="15"/>
       <c r="J99" s="16"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:11">
       <c r="A100" s="11"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -11447,6 +10517,41 @@
       <c r="H100" s="15"/>
       <c r="I100" s="15"/>
       <c r="J100" s="16"/>
+    </row>
+    <row r="101" ht="16.5" spans="1:11">
+      <c r="A101" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F101" s="13">
+        <v>150</v>
+      </c>
+      <c r="G101" s="14">
+        <v>0</v>
+      </c>
+      <c r="H101" s="13">
+        <v>250</v>
+      </c>
+      <c r="I101" s="13">
+        <v>0</v>
+      </c>
+      <c r="J101" s="14">
+        <v>0</v>
+      </c>
+      <c r="K101" s="13">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -11477,16 +10582,16 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:4">
       <c r="A1" s="6" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4">
@@ -11494,643 +10599,643 @@
         <v>54</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B3" s="9">
         <v>17821</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:4">
       <c r="A4" s="8" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="B4" s="9">
         <v>0.02</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4">
       <c r="A5" s="8" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="B5" s="9">
         <v>96</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:4">
       <c r="A6" s="8" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="B6" s="9">
         <v>54</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:4">
       <c r="A7" s="8" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="B7" s="9">
         <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:4">
       <c r="A8" s="8" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="B8" s="9">
         <v>5</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
       <c r="A9" s="8" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="B9" s="9">
         <v>5</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:4">
       <c r="A10" s="8" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="B10" s="9">
         <v>0.25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:4">
       <c r="A11" s="8" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="B11" s="9">
         <v>0.12</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:4">
       <c r="A12" s="8" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B12" s="9">
         <v>3</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:4">
       <c r="A13" s="8" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="B13" s="9">
         <v>600</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="B14" s="9">
         <v>400</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:4">
       <c r="A15" s="8" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="B15" s="9">
         <v>1.5</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:4">
       <c r="A16" s="8" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="B16" s="9">
         <v>18</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:4">
       <c r="A17" s="8" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="B17" s="9">
         <v>0.75</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:4">
       <c r="A18" s="8" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="B18" s="9">
         <v>2</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:4">
       <c r="A19" s="8" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B19" s="9">
         <v>0.3</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B20" s="9">
         <v>1</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:4">
       <c r="A21" s="8" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="B21" s="9">
         <v>0.31</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:4">
       <c r="A22" s="8" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="B22" s="9">
         <v>0.41</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:4">
       <c r="A23" s="8" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="B23" s="9">
         <v>0.25</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:4">
       <c r="A24" s="8" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="B24" s="9">
         <v>1</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="B25" s="9">
         <v>0.3</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:4">
       <c r="A26" s="8" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="B26" s="9">
         <v>0.4</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:4">
       <c r="A27" s="8" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="B27" s="9">
         <v>0.245</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:4">
       <c r="A28" s="8" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="B28" s="9">
         <v>1</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:4">
       <c r="A29" s="8" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="B29" s="9">
         <v>0.93</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:4">
       <c r="A30" s="8" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="B30" s="9">
         <v>0.73</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:4">
       <c r="A31" s="8" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="B31" s="9">
         <v>0.32</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:4">
       <c r="A32" s="8" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="B32" s="9">
         <v>1</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:4">
       <c r="A33" s="8" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="B33" s="9">
         <v>0.52</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:4">
       <c r="A34" s="8" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="B34" s="9">
         <v>0.5</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:4">
       <c r="A35" s="8" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="B35" s="9">
         <v>0.4</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:4">
       <c r="A36" s="8" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B36" s="9">
-        <v>100</v>
+        <v>100000000</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:4">
       <c r="A37" s="8" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="B37" s="9">
         <v>1</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:4">
       <c r="A38" s="8" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="B38" s="9">
         <v>1</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:4">
       <c r="A39" s="8" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="B39" s="9">
         <v>5</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:4">
       <c r="A40" s="8" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B40" s="9">
         <v>10</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:4">
       <c r="A41" s="8" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="B41" s="9">
         <v>10</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:4">
       <c r="A42" s="8" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="B42" s="9">
         <v>1</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:4">
       <c r="A43" s="8" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="B43" s="9">
         <v>10</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:4">
       <c r="A44" s="8" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="B44" s="9">
         <v>0.5</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1" spans="1:4">
       <c r="A45" s="8" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B45" s="9">
         <v>2</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1" spans="1:4">
       <c r="A46" s="8" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B46" s="9">
         <v>30000</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1" spans="1:4">
       <c r="A47" s="8" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="B47" s="9">
         <v>10000</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -12400,16 +11505,16 @@
     </row>
     <row r="101" ht="36" customHeight="1" spans="1:4">
       <c r="A101" s="8" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="B101" s="9">
         <v>2</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameContent.xlsx
+++ b/Config/GameContent.xlsx
@@ -11173,7 +11173,7 @@
         <v>329</v>
       </c>
       <c r="B43" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>249</v>

--- a/Config/GameContent.xlsx
+++ b/Config/GameContent.xlsx
@@ -3424,10 +3424,10 @@
         <v>1.25</v>
       </c>
       <c r="G4" s="14">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="H4" s="14">
-        <v>1.35</v>
+        <v>0.945</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>76</v>
@@ -3462,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="14">
-        <v>0.24</v>
+        <v>0.168</v>
       </c>
       <c r="H5" s="14">
-        <v>0.95</v>
+        <v>0.665</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>82</v>
@@ -3500,10 +3500,10 @@
         <v>2.2</v>
       </c>
       <c r="G6" s="14">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H6" s="14">
-        <v>0.95</v>
+        <v>0.665</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>87</v>
@@ -3538,10 +3538,10 @@
         <v>2.4</v>
       </c>
       <c r="G7" s="14">
-        <v>0.28</v>
+        <v>0.196</v>
       </c>
       <c r="H7" s="14">
-        <v>1</v>
+        <v>0.70</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>92</v>

--- a/Config/GameContent.xlsx
+++ b/Config/GameContent.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17080" activeTab="8"/>
+    <workbookView windowHeight="17080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" r:id="rId1"/>
@@ -1349,12 +1349,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.###"/>
+    <numFmt numFmtId="177" formatCode="0.0#"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -2055,7 +2056,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2091,6 +2092,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3278,7 +3280,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="27" style="1" customWidth="1"/>
@@ -3287,6 +3289,7 @@
     <col min="10" max="11" width="25" style="1" customWidth="1"/>
     <col min="12" max="12" width="30" style="1" customWidth="1"/>
     <col min="13" max="13" width="22" style="1" customWidth="1"/>
+    <col min="14" max="14" width="36" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:13">
@@ -3329,6 +3332,9 @@
       <c r="M1" s="6" t="s">
         <v>58</v>
       </c>
+      <c r="N1" s="6" t="str">
+        <v>生命恢复/点每秒</v>
+      </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:13">
       <c r="A2" s="7" t="s">
@@ -3370,6 +3376,9 @@
       <c r="M2" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="N2" s="7" t="str">
+        <v>healthRegenerationPerSecond</v>
+      </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:13">
       <c r="A3" s="8" t="s">
@@ -3382,7 +3391,7 @@
         <v>74</v>
       </c>
       <c r="D3" s="13">
-        <v>10000000</v>
+        <v>200</v>
       </c>
       <c r="E3" s="13">
         <v>3</v>
@@ -3410,6 +3419,9 @@
       </c>
       <c r="M3" s="13">
         <v>0</v>
+      </c>
+      <c r="N3" s="19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:13">
@@ -3452,6 +3464,9 @@
       <c r="M4" s="13">
         <v>5</v>
       </c>
+      <c r="N4" s="19" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:13">
       <c r="A5" s="8" t="s">
@@ -3493,6 +3508,9 @@
       <c r="M5" s="13">
         <v>5</v>
       </c>
+      <c r="N5" s="19" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:13">
       <c r="A6" s="8" t="s">
@@ -3534,6 +3552,9 @@
       <c r="M6" s="13">
         <v>0</v>
       </c>
+      <c r="N6" s="19" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:13">
       <c r="A7" s="8" t="s">
@@ -3574,6 +3595,9 @@
       </c>
       <c r="M7" s="13">
         <v>0</v>
+      </c>
+      <c r="N7" s="19" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:13">
